--- a/docs/samples/onecare-bulk-upload-template.xlsx
+++ b/docs/samples/onecare-bulk-upload-template.xlsx
@@ -89,6 +89,18 @@
   </si>
   <si>
     <t>현장 사례</t>
+  </si>
+  <si>
+    <t>사진2</t>
+  </si>
+  <si>
+    <t>사진2 설명</t>
+  </si>
+  <si>
+    <t>사진3</t>
+  </si>
+  <si>
+    <t>사진3 설명</t>
   </si>
   <si>
     <t>강남</t>
@@ -224,6 +236,10 @@
     <col min="23" max="23" width="30" customWidth="1"/>
     <col min="24" max="24" width="24" customWidth="1"/>
     <col min="25" max="25" width="40" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="24" customWidth="1"/>
+    <col min="29" max="29" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -302,69 +318,85 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
     </row>
   </sheetData>
 </worksheet>
